--- a/week3/homework-cv-bootstrap-shrinkage.xlsx
+++ b/week3/homework-cv-bootstrap-shrinkage.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="106">
   <si>
     <t xml:space="preserve">[Description] Cross-Validation, Bootstrap &amp; Shrinkage</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t xml:space="preserve">average of 5 folds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your Answer:</t>
   </si>
   <si>
     <t xml:space="preserve">CV(quadratic) =</t>
@@ -971,7 +974,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -1071,64 +1074,72 @@
       <c r="A16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="11"/>
       <c r="E16" s="11"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="5" t="str">
-        <f aca="false">IF(F16="","",IF(ROUND(F16,3)=ROUND(3.2,3),"✓","✗"))</f>
+      <c r="F16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="5" t="str">
+        <f aca="false">IF(G16="","",IF(ROUND(G16,3)=ROUND(3.2,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="11"/>
+        <v>37</v>
+      </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="5" t="str">
-        <f aca="false">IF(F18="","",IF(ROUND(F18,3)=ROUND(2.8,3),"✓","✗"))</f>
+      <c r="F18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="5" t="str">
+        <f aca="false">IF(G18="","",IF(ROUND(G18,3)=ROUND(2.8,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="11"/>
+        <v>38</v>
+      </c>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="5" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))=UPPER("quadratic"),"✓","✗"))</f>
+      <c r="F20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="5" t="str">
+        <f aca="false">IF(G20="","",IF(UPPER(TRIM(G20))=UPPER("quadratic"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="11"/>
+      <c r="D22" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="5" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))=UPPER("linear"),"✓","✗"))</f>
+      <c r="F22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="5" t="str">
+        <f aca="false">IF(G22="","",IF(UPPER(TRIM(G22))=UPPER("linear"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D22:E22"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J22">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1153,7 +1164,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -1164,47 +1175,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1304,54 +1315,60 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="5" t="str">
-        <f aca="false">IF(F18="","",IF(ROUND(F18,3)=ROUND(5.266667,3),"✓","✗"))</f>
+      <c r="F18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="5" t="str">
+        <f aca="false">IF(G18="","",IF(ROUND(G18,3)=ROUND(5.266667,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="11"/>
+      <c r="D20" s="11" t="s">
+        <v>55</v>
+      </c>
       <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="5" t="str">
-        <f aca="false">IF(F20="","",IF(ROUND(F20,3)=ROUND(1.011599,3),"✓","✗"))</f>
+      <c r="F20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="5" t="str">
+        <f aca="false">IF(G20="","",IF(ROUND(G20,3)=ROUND(1.01105,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="11"/>
+      <c r="D22" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="5" t="str">
-        <f aca="false">IF(F22="","",IF(ROUND(F22,3)=ROUND(0.296296,3),"✓","✗"))</f>
+      <c r="F22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="5" t="str">
+        <f aca="false">IF(G22="","",IF(ROUND(G22,3)=ROUND(0.296296,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="D22:E22"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J22">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1376,7 +1393,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1386,38 +1403,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1472,22 +1489,24 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="11" t="s">
+        <v>66</v>
+      </c>
       <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="5" t="str">
-        <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))=UPPER("No"),"✓","✗"))</f>
+      <c r="F18" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="5" t="str">
+        <f aca="false">IF(G18="","",IF(UPPER(TRIM(G18))=UPPER("No"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="D18:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J18">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1512,7 +1531,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="10"/>
@@ -1522,46 +1541,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>3</v>
@@ -1574,7 +1593,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>-1.5</v>
@@ -1587,7 +1606,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>0.4</v>
@@ -1600,7 +1619,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>-0.9</v>
@@ -1613,36 +1632,40 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="11" t="s">
+        <v>80</v>
+      </c>
       <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="5" t="str">
-        <f aca="false">IF(F17="","",IF(ROUND(F17,3)=ROUND(2,3),"✓","✗"))</f>
+      <c r="F17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="5" t="str">
+        <f aca="false">IF(G17="","",IF(ROUND(G17,3)=ROUND(2,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="11"/>
+        <v>81</v>
+      </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="5" t="str">
-        <f aca="false">IF(F19="","",IF(ROUND(F19,3)=ROUND(0,3),"✓","✗"))</f>
+      <c r="F19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="5" t="str">
+        <f aca="false">IF(G19="","",IF(ROUND(G19,3)=ROUND(0,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D19:E19"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J19">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1676,59 +1699,59 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>5.267</v>
@@ -1739,12 +1762,12 @@
         <v>16</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>1.0116</v>
+        <v>1.011</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>0.2963</v>
@@ -1752,41 +1775,41 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>2</v>
@@ -1794,7 +1817,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" s="7" t="n">
         <v>0</v>
